--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488195_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488195_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.9429</v>
+        <v>7.4543</v>
       </c>
       <c r="E2" t="n">
-        <v>10.4546</v>
+        <v>9.138299999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5117</v>
+        <v>-1.684</v>
       </c>
       <c r="G2" t="n">
         <v>4.8367</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4033</v>
+        <v>0.9146</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0854</v>
+        <v>0.7691</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3178</v>
+        <v>0.1455</v>
       </c>
       <c r="V2" t="n">
         <v>1.8883</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>J. PINA GUISADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4805</v>
+        <v>5.8248</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3349</v>
+        <v>6.5648</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8544</v>
+        <v>-0.74</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6572</v>
+        <v>3.8899</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5033</v>
+        <v>4.1202</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8461</v>
+        <v>-0.2304</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0435</v>
+        <v>6.2738</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8776</v>
+        <v>5.4752</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1659</v>
+        <v>0.7986</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3863</v>
+        <v>-2.384</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3743</v>
+        <v>-1.355</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.012</v>
+        <v>-1.029</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1853</v>
+        <v>1.6676</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1759</v>
+        <v>0.2674</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0533</v>
+        <v>0.291</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1226</v>
+        <v>-0.0236</v>
       </c>
       <c r="V3" t="n">
-        <v>2.8327</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>4.091</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PINA GUISADO</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4254</v>
+        <v>5.2858</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5101</v>
+        <v>6.9432</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0847</v>
+        <v>-1.6574</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8899</v>
+        <v>1.6572</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1202</v>
+        <v>3.5033</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2304</v>
+        <v>-1.8461</v>
       </c>
       <c r="J4" t="n">
-        <v>6.2738</v>
+        <v>4.0435</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4752</v>
+        <v>3.8776</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7986</v>
+        <v>0.1659</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.384</v>
+        <v>-2.3863</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.355</v>
+        <v>-0.3743</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.029</v>
+        <v>-2.012</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6676</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R4" t="n">
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1321</v>
+        <v>0.9811</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2363</v>
+        <v>0.6616</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3683</v>
+        <v>0.3196</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.8327</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.091</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9184</v>
+        <v>1.4053</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2964</v>
+        <v>1.6109</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3779</v>
+        <v>-0.2056</v>
       </c>
       <c r="G5" t="n">
         <v>0.2353</v>
@@ -844,13 +844,13 @@
         <v>0.7411</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2565</v>
+        <v>0.7433</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0869</v>
+        <v>0.4014</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1696</v>
+        <v>0.342</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3144</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8237</v>
+        <v>0.9944</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6571</v>
+        <v>0.9508</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1667</v>
+        <v>0.0436</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5889</v>
@@ -922,13 +922,13 @@
         <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3009</v>
+        <v>0.4716</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2189</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5198</v>
+        <v>0.3967</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2086</v>
+        <v>-0.1594</v>
       </c>
       <c r="E9" t="n">
         <v>-0.0143</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1943</v>
+        <v>-0.1451</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5573</v>
@@ -1156,13 +1156,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2072</v>
+        <v>-0.1579</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9986</v>
+        <v>-1.0971</v>
       </c>
       <c r="E10" t="n">
         <v>-0.8635</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1351</v>
+        <v>-0.2336</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6506</v>
@@ -1234,13 +1234,13 @@
         <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2079</v>
+        <v>0.1094</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2079</v>
+        <v>0.1094</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>M. CABEZA RUEDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5764</v>
+        <v>-1.1516</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7269</v>
+        <v>1.674</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8495</v>
+        <v>-2.8256</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2143</v>
+        <v>1.6455</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8519</v>
+        <v>-0.5003</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3624</v>
+        <v>2.1458</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0626</v>
+        <v>5.0268</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5495</v>
+        <v>1.1071</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.487</v>
+        <v>3.9197</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2768</v>
+        <v>-3.3812</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4014</v>
+        <v>-1.6074</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8754</v>
+        <v>-1.7738</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1853</v>
+        <v>-4.6322</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>-6.485</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1117</v>
+        <v>1.8529</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1768</v>
+        <v>0.5767</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4924</v>
+        <v>0.3006</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3156</v>
+        <v>0.276</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6294</v>
+        <v>1.2583</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6294</v>
+        <v>2.8316</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. CABEZA RUEDA</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2108</v>
+        <v>-1.4987</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7379</v>
+        <v>-0.3784</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9487</v>
+        <v>-1.1204</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6455</v>
+        <v>-2.2143</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5003</v>
+        <v>-0.8519</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1458</v>
+        <v>-1.3624</v>
       </c>
       <c r="J12" t="n">
-        <v>5.0268</v>
+        <v>0.0626</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1071</v>
+        <v>0.5495</v>
       </c>
       <c r="L12" t="n">
-        <v>3.9197</v>
+        <v>-0.487</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.3812</v>
+        <v>-2.2768</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6074</v>
+        <v>-1.4014</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7738</v>
+        <v>-0.8754</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.6322</v>
+        <v>0.1853</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.485</v>
+        <v>-0.9264</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8529</v>
+        <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4825</v>
+        <v>-0.0992</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6354</v>
+        <v>-0.1439</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1529</v>
+        <v>0.0448</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2583</v>
+        <v>0.6294</v>
       </c>
       <c r="W12" t="n">
-        <v>2.8316</v>
+        <v>0.6294</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4769</v>
+        <v>-1.9878</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6061</v>
+        <v>-0.0186</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8707</v>
+        <v>-1.9692</v>
       </c>
       <c r="G13" t="n">
         <v>0.8250999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>2.4087</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1167</v>
+        <v>0.3724</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6019</v>
+        <v>-0.0143</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4852</v>
+        <v>0.3867</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8883</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.3213</v>
+        <v>-4.998</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1493</v>
+        <v>0.5957</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.4706</v>
+        <v>-5.5937</v>
       </c>
       <c r="G14" t="n">
         <v>-1.8011</v>
@@ -1546,13 +1546,13 @@
         <v>0.7411</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1878</v>
+        <v>0.1355</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2524</v>
+        <v>0.194</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0646</v>
+        <v>-0.0585</v>
       </c>
       <c r="V14" t="n">
         <v>-3.1471</v>
@@ -1579,25 +1579,25 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7645</v>
+        <v>11.0382</v>
       </c>
       <c r="E15" t="n">
-        <v>26.8957</v>
+        <v>27.1691</v>
       </c>
       <c r="F15" t="n">
-        <v>-16.1309</v>
+        <v>-16.131</v>
       </c>
       <c r="G15" t="n">
-        <v>8.243699999999999</v>
+        <v>8.243700000000002</v>
       </c>
       <c r="H15" t="n">
         <v>9.241300000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9979</v>
+        <v>-0.9979000000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>31.9798</v>
+        <v>31.97979999999999</v>
       </c>
       <c r="K15" t="n">
         <v>19.1933</v>
@@ -1624,13 +1624,13 @@
         <v>13.8965</v>
       </c>
       <c r="S15" t="n">
-        <v>4.0414</v>
+        <v>4.3149</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1515</v>
+        <v>2.425</v>
       </c>
       <c r="U15" t="n">
-        <v>1.89</v>
+        <v>1.8901</v>
       </c>
       <c r="V15" t="n">
         <v>1.2589</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9566</v>
+        <v>2.9411</v>
       </c>
       <c r="E16" t="n">
-        <v>6.4609</v>
+        <v>6.1671</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.5043</v>
+        <v>-3.226</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4379</v>
@@ -1702,13 +1702,13 @@
         <v>3.1499</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3641</v>
+        <v>-0.3796</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1231</v>
+        <v>-0.1706</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4872</v>
+        <v>-0.2089</v>
       </c>
       <c r="V16" t="n">
         <v>3.4616</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7661</v>
+        <v>1.1888</v>
       </c>
       <c r="E18" t="n">
-        <v>3.9166</v>
+        <v>4.5042</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.1505</v>
+        <v>-3.3154</v>
       </c>
       <c r="G18" t="n">
         <v>0.4145</v>
@@ -1858,13 +1858,13 @@
         <v>2.594</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0015</v>
+        <v>-0.5789</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.909</v>
+        <v>-0.3214</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0925</v>
+        <v>-0.2574</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3144</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4069</v>
+        <v>0.5861</v>
       </c>
       <c r="E19" t="n">
-        <v>4.2112</v>
+        <v>4.3091</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.8043</v>
+        <v>-3.723</v>
       </c>
       <c r="G19" t="n">
         <v>0.0866</v>
@@ -1936,13 +1936,13 @@
         <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0476</v>
+        <v>-0.8683</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3109</v>
+        <v>-0.2129</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7367</v>
+        <v>-0.6554</v>
       </c>
       <c r="V19" t="n">
         <v>3.7766</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. LOPEZ BURRERO</t>
+          <t>V. PIETUKHOV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2147</v>
+        <v>-0.0021</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>4.3973</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2147</v>
+        <v>-4.3994</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2147</v>
+        <v>0.6088</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2147</v>
+        <v>0.7887</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.1798</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>5.0034</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>3.4784</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.525</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2147</v>
+        <v>-4.3945</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2147</v>
+        <v>-2.6897</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-1.7048</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0.2229</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.0059</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.2288</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.293</v>
+        <v>-0.0473</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2793</v>
+        <v>0.3773</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5723</v>
+        <v>-0.4246</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1749</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9709</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5471</v>
+        <v>-0.4492</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4238</v>
+        <v>-0.2761</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. PIETUKHOV</t>
+          <t>D. LOPEZ BURRERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4522</v>
+        <v>-0.2147</v>
       </c>
       <c r="E22" t="n">
-        <v>4.2994</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.7515</v>
+        <v>-0.2147</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6088</v>
+        <v>-0.2147</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7887</v>
+        <v>-0.2147</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1798</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>5.0034</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4784</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.525</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.3945</v>
+        <v>-0.2147</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.6897</v>
+        <v>-0.2147</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7048</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.673</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.092</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.581</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2371</v>
+        <v>-3.0216</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-1.1122</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7124</v>
+        <v>-1.9094</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6239</v>
@@ -2248,13 +2248,13 @@
         <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0898</v>
+        <v>0.3053</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6491</v>
+        <v>0.0616</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4407</v>
+        <v>0.2437</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2589</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.6326</v>
+        <v>-6.289</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8671</v>
+        <v>-2.6713</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.7655</v>
+        <v>-3.6177</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9563</v>
@@ -2326,13 +2326,13 @@
         <v>2.2234</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0468</v>
+        <v>-0.7032</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.766</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2808</v>
+        <v>-0.1331</v>
       </c>
       <c r="V24" t="n">
         <v>-3.1471</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6528</v>
+        <v>-6.8412</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2328</v>
+        <v>-1.4287</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.42</v>
+        <v>-5.4125</v>
       </c>
       <c r="G25" t="n">
         <v>-4.5339</v>
@@ -2404,13 +2404,13 @@
         <v>1.6676</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0274</v>
+        <v>-0.2158</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0373</v>
+        <v>-0.2331</v>
       </c>
       <c r="U25" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0174</v>
       </c>
       <c r="V25" t="n">
         <v>-2.8327</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.7645</v>
+        <v>-10.1116</v>
       </c>
       <c r="E26" t="n">
         <v>16.1311</v>
       </c>
       <c r="F26" t="n">
-        <v>-26.8955</v>
+        <v>-26.2427</v>
       </c>
       <c r="G26" t="n">
         <v>-8.243400000000001</v>
@@ -2482,13 +2482,13 @@
         <v>16.6758</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.0415</v>
+        <v>-3.3887</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.8901</v>
+        <v>-1.8898</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.1514</v>
+        <v>-1.4986</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2588</v>
